--- a/src/result/lfw/svm_linear_report.xlsx
+++ b/src/result/lfw/svm_linear_report.xlsx
@@ -413,237 +413,182 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>f1-score</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="A2" t="n">
+        <v>0.625</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="D2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E2" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A3" t="n">
+        <v>0.8382352941176471</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8285714285714286</v>
+        <v>0.8382352941176471</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8529411764705882</v>
+        <v>0.8382352941176471</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8405797101449275</v>
-      </c>
-      <c r="E3" t="n">
         <v>68</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A4" t="n">
+        <v>0.6451612903225806</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7540983606557377</v>
-      </c>
-      <c r="E4" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A5" t="n">
+        <v>0.8677685950413223</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8898305084745762</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8502024291497976</v>
       </c>
       <c r="D5" t="n">
-        <v>0.860655737704918</v>
-      </c>
-      <c r="E5" t="n">
         <v>126</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A6" t="n">
+        <v>0.6538461538461539</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6792452830188679</v>
-      </c>
-      <c r="E6" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="A7" t="n">
+        <v>0.9285714285714286</v>
       </c>
       <c r="B7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="D7" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E7" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.8571428571428571</v>
-      </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9230769230769231</v>
-      </c>
-      <c r="E8" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A9" t="n">
+        <v>0.7872340425531915</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7608695652173914</v>
+        <v>0.8809523809523809</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8314606741573034</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7954545454545454</v>
-      </c>
-      <c r="E9" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>accuracy</t>
-        </is>
+      <c r="A10" t="n">
+        <v>0.8041543026706232</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8100890207715133</v>
+        <v>0.8041543026706232</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8100890207715133</v>
+        <v>0.8041543026706232</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8100890207715133</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.8100890207715133</v>
+        <v>0.8041543026706232</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>macro avg</t>
-        </is>
+      <c r="A11" t="n">
+        <v>0.7753699576993976</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7864145400238209</v>
+        <v>0.7816849250219022</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7888523361658829</v>
+        <v>0.7739851668150227</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7785138200069899</v>
-      </c>
-      <c r="E11" t="n">
         <v>337</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>weighted avg</t>
-        </is>
+      <c r="A12" t="n">
+        <v>0.8091195167894512</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8222371908425218</v>
+        <v>0.8041543026706232</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8100890207715133</v>
+        <v>0.8043160182189057</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8114621599894675</v>
-      </c>
-      <c r="E12" t="n">
         <v>337</v>
       </c>
     </row>
